--- a/artfynd/A 40209-2021 artfynd.xlsx
+++ b/artfynd/A 40209-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40209-2021 artfynd.xlsx
+++ b/artfynd/A 40209-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96277079</v>
+        <v>96277078</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633565.578604578</v>
+        <v>633500</v>
       </c>
       <c r="R2" t="n">
-        <v>7092749.490756528</v>
+        <v>7092312</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
+          <t>Emil Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,50 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96277078</v>
+        <v>98645521</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>1963</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Videticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Antrodia macra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sommerf.) Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Predikstolberget, Ås lm</t>
+          <t>Mesjöberget, Åsele, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633500.0415971982</v>
+        <v>633765</v>
       </c>
       <c r="R3" t="n">
-        <v>7092312.50991219</v>
+        <v>7092661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,27 +859,22 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,6 +891,11 @@
       <c r="AO3" t="inlineStr">
         <is>
           <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,12 +920,7 @@
         <v>96277080</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633699.485285141</v>
+        <v>633699</v>
       </c>
       <c r="R4" t="n">
-        <v>7092608.150485338</v>
+        <v>7092608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,19 +985,9 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,10 +1022,318 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Emil Larsson, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96277079</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Predikstolberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>633566</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092749</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96277081</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Predikstolberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633770</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092657</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96277084</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Predikstolberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633878</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7092795</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>

--- a/artfynd/A 40209-2021 artfynd.xlsx
+++ b/artfynd/A 40209-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96277078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98645521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96277080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96277079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96277081</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,8 +1368,21 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96277084</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>